--- a/artfynd/A 45401-2023 artfynd.xlsx
+++ b/artfynd/A 45401-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45401-2023 artfynd.xlsx
+++ b/artfynd/A 45401-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>128391</v>
       </c>
       <c r="B2" t="n">
-        <v>104642</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>368675.4717216147</v>
+        <v>368675</v>
       </c>
       <c r="R2" t="n">
-        <v>6619109.309828948</v>
+        <v>6619109</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2004-08-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2004-08-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -806,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3058641</v>
+        <v>3058637</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -855,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>368674.2996012362</v>
+        <v>368674</v>
       </c>
       <c r="R3" t="n">
-        <v>6619047.19817584</v>
+        <v>6619047</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -883,29 +863,14 @@
           <t>Arvika</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>S-Arv-0416</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2011-12-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -935,7 +900,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Värmland Floraväktarna</t>
+          <t>Per Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -943,11 +908,7 @@
           <t>Per Larsson, Elvi Eriksson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
